--- a/AAII_Financials/Yearly/RLAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RLAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>RLAY</t>
   </si>
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>259500</v>
+        <v>257200</v>
       </c>
       <c r="E9" s="3">
         <v>315400</v>
@@ -817,7 +817,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-244200</v>
+        <v>-241900</v>
       </c>
       <c r="E10" s="3">
         <v>-305400</v>
@@ -970,8 +970,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
         <v>-13200</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>318100</v>
+        <v>315800</v>
       </c>
       <c r="E17" s="3">
         <v>395700</v>
@@ -1122,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-302700</v>
+        <v>-300400</v>
       </c>
       <c r="E18" s="3">
         <v>-385700</v>
@@ -1231,7 +1231,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-300000</v>
+        <v>-297700</v>
       </c>
       <c r="E21" s="3">
         <v>-380200</v>
